--- a/docs/deliverables/out/Programme/FitGap/BIBS_FitGap_BRD-05_Accounting_Disbursement_ACSL_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/FitGap/BIBS_FitGap_BRD-05_Accounting_Disbursement_ACSL_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Counts of the Fit-Gap sheet; 276 rows in scope.</t>
+          <t>Counts of the Fit-Gap sheet; 273 rows in scope.</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
@@ -3120,113 +3120,113 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>FRBS 3.3.0</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="22" t="inlineStr">
         <is>
           <t>FR-AC-050</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>Upload bank files and reconcile automatically</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>Black (BRD)</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>Fit</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>Grey (Integration)</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
         <is>
           <t>ACC-011</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>Statement import (BDO, BPI, Metrobank, generic), six auto-match rules, adjustments, reconciliation statement with approval. BIBS screens: SCR-AC-14, SCR-AC-15, SCR-AC-16.</t>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>Depends on an interface with another BDO or third-party system; Integration scope. BIBS screens: SCR-AC-14, SCR-AC-15, SCR-AC-16.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>FRBS 3.3.1</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>FR-AC-050</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>Upload bank files and reconcile automatically</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>Black (BRD)</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Fit</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>Grey (Integration)</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>ACC-011</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>Statement import (BDO, BPI, Metrobank, generic), six auto-match rules, adjustments, reconciliation statement with approval. BIBS screens: SCR-AC-14, SCR-AC-15, SCR-AC-16.</t>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>Depends on an interface with another BDO or third-party system; Integration scope. BIBS screens: SCR-AC-14, SCR-AC-15, SCR-AC-16.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>FRBS 3.3.2</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>FR-AC-050</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>Upload bank files and reconcile automatically</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>Black (BRD)</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Fit</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>Grey (Integration)</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>ACC-011</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
-        <is>
-          <t>Statement import (BDO, BPI, Metrobank, generic), six auto-match rules, adjustments, reconciliation statement with approval. BIBS screens: SCR-AC-14, SCR-AC-15, SCR-AC-16.</t>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>Depends on an interface with another BDO or third-party system; Integration scope. BIBS screens: SCR-AC-14, SCR-AC-15, SCR-AC-16.</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Counts of the Fit-Gap sheet; 276 rows in scope.</t>
+          <t>Counts of the Fit-Gap sheet; 273 rows in scope.</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
